--- a/Luban/Config/Datas/Levels/L13/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L13/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L13 W1/25; N=43; EHP=259.204000; normal:17x21,normal:18x22</t>
+          <t>L13 W1/25; N=43; EHP=599.665541; normal:17x21,normal:18x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L13 W2/25; N=49; EHP=309.284021; normal:17x25,normal:18x24</t>
+          <t>L13 W2/25; N=49; EHP=715.525108; normal:17x25,normal:18x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3584136,3584673,3584019,3584136,3584673,3584019,3584136,3584673,3584091,3584136,3584673,3584099,3584136,3584673,3584099,3584136,3584673,3584107,3584136,3584673,3584115,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144</t>
+          <t>3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584673,3584136,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144,3584144</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L13 W3/25; N=55; EHP=384.055936; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x16,normal:18x17,swarm:84x15</t>
+          <t>L13 W3/25; N=55; EHP=963.035454; normal:17x16,normal:18x24,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3586136,3586673,3586019,3586136,3586673,3586019,3586136,3586673,3586091,3586136,3586673,3586099,3586136,3586673,3586107,3586136,3586673,3586107,3586136,3586673,3586115,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586136,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144</t>
+          <t>3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586673,3586136,3586136,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586144,3586136,3586136,3586136,3586136,3586136,3586136,3586136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L13 W4/25; N=61; EHP=490.485701; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x19,normal:18x18,swarm:84x17</t>
+          <t>L13 W4/25; N=61; EHP=1220.059773; normal:17x26,normal:18x18,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3588136,3588673,3588019,3588668,3588136,3588673,3588091,3588668,3588136,3588673,3588091,3588668,3588136,3588673,3588099,3588668,3588136,3588673,3588107,3588868,3588136,3588673,3588107,3588868,3588136,3588673,3588115,3588868,3588136,3588673,3588115,3588988,3588136,3588673,3588988,3588136,3588673,3588988,3588136,3588673,3588136,3588673,3588136,3588673,3588136,3588673,3588136,3588673,3588144,3588673,3588144,3588673,3588144,3588673,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144</t>
+          <t>3588136,3588019,3588019,3588668,3588136,3588091,3588091,3588668,3588136,3588091,3588091,3588668,3588136,3588099,3588099,3588668,3588136,3588107,3588107,3588868,3588136,3588107,3588107,3588868,3588136,3588115,3588115,3588868,3588136,3588115,3588115,3588988,3588136,3588673,3588988,3588136,3588673,3588988,3588136,3588673,3588136,3588673,3588136,3588673,3588136,3588673,3588136,3588673,3588144,3588673,3588144,3588673,3588144,3588673,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144,3588144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L13 W5/25; N=67; EHP=927.887339; air:2x1,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x15,normal:18x16,medium:83x4,swarm:84x18,medium:108x3,medium:123x3</t>
+          <t>L13 W5/25; N=67; EHP=2173.786878; air:2x2,air:11x4,air:12x2,air:13x4,air:14x4,medium:83x4,medium:108x3,medium:123x3,normal:17x15,normal:18x16,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3590136,3590673,3590242,3590019,3590668,3590136,3590673,3590242,3590019,3590668,3590136,3590673,3590466,3590091,3590668,3590136,3590673,3590466,3590091,3590868,3590136,3590673,3590514,3590099,3590868,3590136,3590673,3590514,3590099,3590868,3590136,3590673,3590786,3590107,3590988,3590136,3590673,3590786,3590115,3590988,3590136,3590673,3590115,3590988,3590136,3590673,3590988,3590136,3590673,3590136,3590673,3590136,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590144,3590144,3590144,3590144,3590144</t>
+          <t>3590136,3590019,3590242,3590019,3590668,3590136,3590019,3590242,3590019,3590668,3590136,3590091,3590466,3590091,3590668,3590136,3590091,3590466,3590091,3590868,3590136,3590099,3590514,3590099,3590868,3590136,3590099,3590514,3590099,3590868,3590136,3590107,3590786,3590107,3590988,3590136,3590115,3590786,3590115,3590988,3590136,3590115,3590115,3590988,3590136,3590673,3590988,3590136,3590673,3590136,3590673,3590136,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590673,3590144,3590144,3590144,3590144,3590144,3590144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L13 W6/25; N=73; EHP=947.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x13,normal:18x13,fast:30x2,fast:58x2,fast:64x2,medium:83x3,swarm:84x20,fast:98x2,medium:108x3,medium:123x4</t>
+          <t>L13 W6/25; N=73; EHP=2220.369542; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x2,medium:83x3,medium:108x3,medium:123x4,normal:17x13,normal:18x13,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3592136,3592673,3592242,3592019,3592668,3592136,3592673,3592242,3592019,3592668,3592136,3592673,3592242,3592091,3592668,3592136,3592673,3592466,3592099,3592668,3592136,3592673,3592466,3592099,3592868,3592136,3592673,3592514,3592107,3592868,3592136,3592673,3592514,3592107,3592868,3592136,3592673,3592786,3592115,3592868,3592136,3592673,3592786,3592115,3592988,3592136,3592673,3592988,3592136,3592673,3592988,3592136,3592673,3592136,3592673,3592136,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592144,3592144,3592144,3592144,3592144</t>
+          <t>3592136,3592019,3592242,3592019,3592668,3592136,3592019,3592242,3592019,3592668,3592136,3592091,3592242,3592091,3592668,3592136,3592099,3592466,3592099,3592668,3592136,3592099,3592466,3592099,3592868,3592136,3592107,3592514,3592107,3592868,3592136,3592107,3592514,3592107,3592868,3592136,3592115,3592786,3592115,3592868,3592136,3592115,3592786,3592115,3592988,3592136,3592673,3592988,3592136,3592673,3592988,3592136,3592673,3592136,3592673,3592136,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592673,3592144,3592144,3592144,3592144,3592144,3592144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L13 W7/25; N=79; EHP=1070.000000; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x14,normal:18x14,fast:30x3,fast:58x2,fast:64x2,medium:83x4,swarm:84x22,fast:98x2,medium:108x4,medium:123x3</t>
+          <t>L13 W7/25; N=79; EHP=2506.077951; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x2,fast:98x2,medium:83x4,medium:108x4,medium:123x3,normal:17x14,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3594136,3594673,3594242,3594019,3594668,3594136,3594673,3594242,3594019,3594668,3594136,3594673,3594466,3594091,3594668,3594136,3594673,3594466,3594091,3594668,3594136,3594673,3594466,3594099,3594868,3594136,3594673,3594514,3594099,3594868,3594136,3594673,3594514,3594107,3594868,3594136,3594673,3594786,3594107,3594868,3594136,3594673,3594786,3594115,3594988,3594136,3594673,3594786,3594115,3594988,3594136,3594673,3594988,3594136,3594673,3594988,3594136,3594673,3594136,3594673,3594136,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594144,3594144,3594144,3594144,3594144,3594144</t>
+          <t>3594136,3594019,3594242,3594019,3594668,3594136,3594019,3594242,3594019,3594668,3594136,3594091,3594466,3594091,3594668,3594136,3594091,3594466,3594091,3594668,3594136,3594099,3594466,3594099,3594868,3594136,3594099,3594514,3594099,3594868,3594136,3594107,3594514,3594107,3594868,3594136,3594107,3594786,3594107,3594868,3594136,3594115,3594786,3594115,3594988,3594136,3594115,3594786,3594115,3594988,3594136,3594673,3594988,3594136,3594673,3594988,3594136,3594673,3594136,3594673,3594136,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594673,3594144,3594144,3594144,3594144,3594144,3594144,3594144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L13 W8/25; N=85; EHP=1376.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x23,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L13 W8/25; N=85; EHP=3223.990538; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3596136,3596673,3596242,3596019,3596668,3596136,3596673,3596242,3596019,3596668,3596136,3596673,3596466,3596019,3596668,3596136,3596673,3596466,3596091,3596668,3596136,3596673,3596466,3596091,3596868,3596136,3596673,3596514,3596099,3596868,3596136,3596673,3596514,3596099,3596868,3596136,3596673,3596514,3596107,3596868,3596136,3596673,3596786,3596107,3596988,3596136,3596673,3596786,3596115,3596988,3596136,3596673,3596115,3596988,3596136,3596673,3596988,3596136,3596673,3596988,3596136,3596673,3596136,3596673,3596136,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596144,3596144,3596144,3596144,3596144,3596144</t>
+          <t>3596136,3596019,3596242,3596019,3596668,3596136,3596019,3596242,3596019,3596668,3596136,3596019,3596466,3596019,3596668,3596136,3596091,3596466,3596091,3596668,3596136,3596091,3596466,3596091,3596868,3596136,3596099,3596514,3596099,3596868,3596136,3596099,3596514,3596099,3596868,3596136,3596107,3596514,3596107,3596868,3596136,3596107,3596786,3596107,3596988,3596136,3596115,3596786,3596115,3596988,3596136,3596115,3596115,3596988,3596136,3596673,3596988,3596136,3596673,3596988,3596136,3596673,3596136,3596673,3596136,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596673,3596144,3596144,3596144,3596144,3596144,3596144,3596144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L13 W9/25; N=91; EHP=1757.000000; air:2x3,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x25,fast:98x2,medium:108x4,medium:123x5</t>
+          <t>L13 W9/25; N=91; EHP=4118.156316; air:2x6,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x5,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3598136,3598673,3598242,3598019,3598668,3598136,3598673,3598242,3598019,3598668,3598136,3598673,3598242,3598091,3598668,3598136,3598673,3598466,3598091,3598668,3598136,3598673,3598466,3598091,3598668,3598136,3598673,3598514,3598099,3598868,3598136,3598673,3598514,3598099,3598868,3598136,3598673,3598514,3598107,3598868,3598136,3598673,3598786,3598107,3598868,3598136,3598673,3598786,3598107,3598868,3598136,3598673,3598786,3598115,3598988,3598136,3598673,3598115,3598988,3598136,3598673,3598988,3598136,3598673,3598988,3598136,3598673,3598136,3598673,3598136,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598144,3598144,3598144,3598144,3598144</t>
+          <t>3598136,3598019,3598242,3598019,3598668,3598136,3598019,3598242,3598019,3598668,3598136,3598091,3598242,3598091,3598668,3598136,3598091,3598466,3598091,3598668,3598136,3598091,3598466,3598091,3598668,3598136,3598099,3598514,3598099,3598868,3598136,3598099,3598514,3598099,3598868,3598136,3598107,3598514,3598107,3598868,3598136,3598107,3598786,3598107,3598868,3598136,3598107,3598786,3598107,3598868,3598136,3598115,3598786,3598115,3598988,3598136,3598115,3598115,3598988,3598136,3598673,3598988,3598136,3598673,3598988,3598136,3598673,3598136,3598673,3598136,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598673,3598144,3598144,3598144,3598144,3598144,3598144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L13 W10/25; N=97; EHP=3242.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x16,fast:30x3,fast:58x2,fast:64x3,medium:83x5,swarm:84x27,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L13 W10/25; N=97; EHP=7601.345122; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x4,normal:17x17,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3600136,3600673,3600242,3600019,3600668,3600253,3600136,3600673,3600242,3600019,3600668,3600325,3600136,3600673,3600242,3600091,3600668,3600541,3600136,3600673,3600466,3600091,3600668,3600565,3600136,3600673,3600466,3600091,3600668,3600645,3600136,3600673,3600466,3600099,3600868,3600645,3600136,3600673,3600514,3600099,3600868,3600693,3600136,3600673,3600514,3600107,3600868,3600709,3600136,3600673,3600514,3600107,3600868,3600709,3600136,3600673,3600786,3600115,3600868,3601021,3600136,3600673,3600786,3600115,3600988,3600136,3600673,3600786,3600115,3600988,3600136,3600673,3600988,3600144,3600673,3600988,3600144,3600673,3600988,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600673,3600673</t>
+          <t>3600136,3600019,3600242,3600019,3600668,3600253,3600136,3600019,3600242,3600019,3600668,3600325,3600136,3600091,3600242,3600091,3600668,3600541,3600136,3600091,3600466,3600091,3600668,3600565,3600136,3600091,3600466,3600091,3600668,3600645,3600136,3600099,3600466,3600099,3600868,3600645,3600136,3600099,3600514,3600099,3600868,3600693,3600136,3600107,3600514,3600107,3600868,3600709,3600136,3600107,3600514,3600107,3600868,3600709,3600136,3600115,3600786,3600115,3600868,3601021,3600136,3600115,3600786,3600115,3600988,3600136,3600115,3600786,3600115,3600988,3600136,3600673,3600988,3600144,3600673,3600988,3600144,3600673,3600988,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600144,3600673,3600673,3600673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L13 W11/25; N=103; EHP=3307.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x28,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L13 W11/25; N=103; EHP=7736.269769; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x13,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3602136,3602673,3602242,3602019,3602668,3602253,3602136,3602673,3602242,3602019,3602668,3602325,3602136,3602673,3602242,3602019,3602668,3602541,3602136,3602673,3602466,3602091,3602668,3602565,3602136,3602673,3602466,3602091,3602668,3602645,3602136,3602673,3602466,3602099,3602868,3602645,3602136,3602673,3602514,3602099,3602868,3602693,3602136,3602673,3602514,3602099,3602868,3602693,3602136,3602673,3602514,3602107,3602868,3602709,3602136,3602673,3602786,3602107,3602868,3603021,3602136,3602673,3602786,3602115,3602988,3602136,3602673,3602786,3602115,3602988,3602136,3602673,3602786,3602115,3602988,3602136,3602673,3602988,3602144,3602673,3602988,3602144,3602673,3602988,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602673,3602673,3602673</t>
+          <t>3602136,3602019,3602242,3602019,3602668,3602253,3602136,3602019,3602242,3602019,3602668,3602325,3602136,3602019,3602242,3602019,3602668,3602541,3602136,3602091,3602466,3602091,3602668,3602565,3602136,3602091,3602466,3602091,3602668,3602645,3602136,3602099,3602466,3602099,3602868,3602645,3602136,3602099,3602514,3602099,3602868,3602693,3602136,3602099,3602514,3602099,3602868,3602693,3602136,3602107,3602514,3602107,3602868,3602709,3602136,3602107,3602786,3602107,3602868,3603021,3602136,3602115,3602786,3602115,3602988,3602136,3602115,3602786,3602115,3602988,3602136,3602115,3602786,3602115,3602988,3602136,3602673,3602988,3602144,3602673,3602988,3602144,3602673,3602988,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602144,3602673,3602673,3602673,3602673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L13 W12/25; N=109; EHP=3423.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x13,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x30,heavy:86x2,heavy:88x1,fast:98x4,medium:108x5,medium:123x6,heavy:127x1</t>
+          <t>L13 W12/25; N=109; EHP=8010.500043; air:2x6,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x5,medium:108x5,medium:123x6,normal:17x14,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3604136,3604673,3604242,3604019,3604668,3604253,3604136,3604673,3604242,3604019,3604668,3604253,3604136,3604673,3604242,3604019,3604668,3604325,3604136,3604673,3604466,3604091,3604668,3604325,3604136,3604673,3604466,3604091,3604668,3604541,3604136,3604673,3604466,3604091,3604668,3604565,3604136,3604673,3604466,3604099,3604868,3604645,3604136,3604673,3604514,3604099,3604868,3604693,3604136,3604673,3604514,3604099,3604868,3604693,3604136,3604673,3604514,3604107,3604868,3604709,3604136,3604673,3604786,3604107,3604868,3605021,3604136,3604673,3604786,3604107,3604868,3604136,3604673,3604786,3604115,3604988,3604136,3604673,3604115,3604988,3604144,3604673,3604988,3604144,3604673,3604988,3604144,3604673,3604988,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604673,3604673,3604673,3604673</t>
+          <t>3604136,3604019,3604242,3604019,3604668,3604253,3604136,3604019,3604242,3604019,3604668,3604253,3604136,3604019,3604242,3604019,3604668,3604325,3604136,3604091,3604466,3604091,3604668,3604325,3604136,3604091,3604466,3604091,3604668,3604541,3604136,3604091,3604466,3604091,3604668,3604565,3604136,3604099,3604466,3604099,3604868,3604645,3604136,3604099,3604514,3604099,3604868,3604693,3604136,3604099,3604514,3604099,3604868,3604693,3604136,3604107,3604514,3604107,3604868,3604709,3604136,3604107,3604786,3604107,3604868,3605021,3604136,3604107,3604786,3604107,3604868,3604136,3604115,3604786,3604115,3604988,3604136,3604115,3604115,3604988,3604144,3604673,3604988,3604144,3604673,3604988,3604144,3604673,3604988,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604144,3604673,3604673,3604673,3604673,3604673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L13 W13/25; N=115; EHP=4176.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x32,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x5,heavy:127x1</t>
+          <t>L13 W13/25; N=115; EHP=9774.551134; air:2x6,air:11x6,air:12x6,air:13x6,air:14x4,fast:30x3,fast:58x4,fast:64x3,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x6,medium:108x6,medium:123x5,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3606136,3606673,3606242,3606019,3606668,3606253,3606136,3606673,3606242,3606019,3606668,3606253,3606136,3606673,3606242,3606019,3606668,3606325,3606136,3606673,3606242,3606091,3606668,3606325,3606136,3606673,3606466,3606091,3606668,3606541,3606136,3606673,3606466,3606091,3606668,3606565,3606136,3606673,3606466,3606099,3606868,3606565,3606136,3606673,3606514,3606099,3606868,3606645,3606136,3606673,3606514,3606099,3606868,3606693,3606136,3606673,3606514,3606107,3606868,3606709,3606136,3606673,3606514,3606107,3606868,3607021,3606136,3606673,3606786,3606107,3606868,3607021,3606136,3606673,3606786,3606115,3606988,3606136,3606673,3606786,3606115,3606988,3606136,3606673,3606115,3606988,3606144,3606673,3606988,3606144,3606673,3606988,3606144,3606673,3606988,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606673,3606673,3606673,3606673</t>
+          <t>3606136,3606019,3606242,3606019,3606668,3606253,3606136,3606019,3606242,3606019,3606668,3606253,3606136,3606019,3606242,3606019,3606668,3606325,3606136,3606091,3606242,3606091,3606668,3606325,3606136,3606091,3606466,3606091,3606668,3606541,3606136,3606091,3606466,3606091,3606668,3606565,3606136,3606099,3606466,3606099,3606868,3606565,3606136,3606099,3606514,3606099,3606868,3606645,3606136,3606099,3606514,3606099,3606868,3606693,3606136,3606107,3606514,3606107,3606868,3606709,3606136,3606107,3606514,3606107,3606868,3607021,3606136,3606107,3606786,3606107,3606868,3607021,3606136,3606115,3606786,3606115,3606988,3606136,3606115,3606786,3606115,3606988,3606136,3606115,3606115,3606988,3606144,3606673,3606988,3606144,3606673,3606988,3606144,3606673,3606988,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606144,3606673,3606673,3606673,3606673,3606673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L13 W14/25; N=121; EHP=5039.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x14,fast:30x4,heavy:31x2,heavy:40x2,fast:58x3,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x33,heavy:86x1,heavy:88x1,fast:98x3,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L13 W14/25; N=121; EHP=11796.341603; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3608136,3608673,3608242,3608019,3608668,3608253,3608542,3608136,3608673,3608242,3608019,3608668,3608325,3608136,3608673,3608242,3608019,3608668,3608325,3608136,3608673,3608242,3608091,3608668,3608541,3608136,3608673,3608466,3608091,3608668,3608541,3608136,3608673,3608466,3608091,3608668,3608565,3608136,3608673,3608466,3608099,3608868,3608565,3608136,3608673,3608466,3608099,3608868,3608645,3608136,3608673,3608514,3608099,3608868,3608693,3608136,3608673,3608514,3608107,3608868,3608709,3608136,3608673,3608514,3608107,3608868,3609021,3608136,3608673,3608786,3608107,3608868,3609021,3608136,3608673,3608786,3608115,3608988,3608136,3608673,3608786,3608115,3608988,3608136,3608673,3608786,3608115,3608988,3608144,3608673,3608988,3608144,3608673,3608988,3608144,3608673,3608988,3608144,3608673,3608988,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608673,3608673,3608673,3608673,3608673</t>
+          <t>3608136,3608019,3608242,3608019,3608668,3608253,3608542,3608136,3608019,3608242,3608019,3608668,3608325,3608136,3608019,3608242,3608019,3608668,3608325,3608136,3608091,3608242,3608091,3608668,3608541,3608136,3608091,3608466,3608091,3608668,3608541,3608136,3608091,3608466,3608091,3608668,3608565,3608136,3608099,3608466,3608099,3608868,3608565,3608136,3608099,3608466,3608099,3608868,3608645,3608136,3608099,3608514,3608099,3608868,3608693,3608136,3608107,3608514,3608107,3608868,3608709,3608136,3608107,3608514,3608107,3608868,3609021,3608136,3608107,3608786,3608107,3608868,3609021,3608136,3608115,3608786,3608115,3608988,3608136,3608115,3608786,3608115,3608988,3608136,3608115,3608786,3608115,3608988,3608144,3608673,3608988,3608144,3608673,3608988,3608144,3608673,3608988,3608144,3608673,3608988,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608144,3608673,3608673,3608673,3608673,3608673,3608673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L13 W15/25; N=127; EHP=8795.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x3,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x1,heavy:88x1,fast:98x4,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L13 W15/25; N=127; EHP=20571.963876; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x3,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x7,normal:17x15,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3610136,3610673,3610242,3610019,3610668,3610253,3610136,3610673,3610242,3610019,3610668,3610325,3610136,3610673,3610242,3610019,3610668,3610541,3610136,3610673,3610466,3610091,3610668,3610541,3610136,3610673,3610466,3610091,3610668,3610565,3610136,3610673,3610466,3610091,3610668,3610565,3610136,3610673,3610466,3610091,3610868,3610645,3610136,3610673,3610514,3610099,3610868,3610645,3610136,3610673,3610514,3610099,3610868,3610693,3610136,3610673,3610514,3610099,3610868,3610709,3610136,3610673,3610514,3610107,3610868,3610709,3610136,3610673,3610786,3610107,3610868,3611021,3610136,3610673,3610786,3610107,3610868,3611021,3610136,3610673,3610786,3610115,3610988,3610136,3610673,3610786,3610115,3610988,3610136,3610673,3610115,3610988,3610136,3610673,3610988,3610144,3610673,3610988,3610144,3610673,3610988,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610673,3610673,3610673,3610673</t>
+          <t>3610136,3610019,3610242,3610019,3610668,3610253,3610136,3610019,3610242,3610019,3610668,3610325,3610136,3610019,3610242,3610019,3610668,3610541,3610136,3610091,3610466,3610091,3610668,3610541,3610136,3610091,3610466,3610091,3610668,3610565,3610136,3610091,3610466,3610091,3610668,3610565,3610136,3610091,3610466,3610091,3610868,3610645,3610136,3610099,3610514,3610099,3610868,3610645,3610136,3610099,3610514,3610099,3610868,3610693,3610136,3610099,3610514,3610099,3610868,3610709,3610136,3610107,3610514,3610107,3610868,3610709,3610136,3610107,3610786,3610107,3610868,3611021,3610136,3610107,3610786,3610107,3610868,3611021,3610136,3610115,3610786,3610115,3610988,3610136,3610115,3610786,3610115,3610988,3610136,3610115,3610115,3610988,3610136,3610673,3610988,3610144,3610673,3610988,3610144,3610673,3610988,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610144,3610673,3610673,3610673,3610673,3610673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L13 W16/25; N=133; EHP=8971.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x3,normal:17x17,normal:18x16,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x6,swarm:84x37,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L13 W16/25; N=133; EHP=20995.111842; air:2x6,air:11x8,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x7,medium:123x6,normal:17x17,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3612136,3612673,3612242,3612019,3612668,3612253,3612136,3612673,3612242,3612019,3612668,3612325,3612136,3612673,3612242,3612019,3612668,3612541,3612136,3612673,3612242,3612091,3612668,3612541,3612136,3612673,3612466,3612091,3612668,3612565,3612136,3612673,3612466,3612091,3612668,3612565,3612136,3612673,3612466,3612099,3612668,3612645,3612136,3612673,3612466,3612099,3612868,3612645,3612136,3612673,3612514,3612099,3612868,3612693,3612136,3612673,3612514,3612099,3612868,3612693,3612136,3612673,3612514,3612107,3612868,3612709,3612136,3612673,3612514,3612107,3612868,3612709,3612136,3612673,3612786,3612107,3612868,3613021,3612136,3612673,3612786,3612115,3612988,3612136,3612673,3612786,3612115,3612988,3612136,3612673,3612786,3612115,3612988,3612136,3612673,3612115,3612988,3612144,3612673,3612988,3612144,3612673,3612988,3612144,3612673,3612988,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612673,3612673,3612673</t>
+          <t>3612136,3612019,3612242,3612019,3612668,3612253,3612136,3612019,3612242,3612019,3612668,3612325,3612136,3612019,3612242,3612019,3612668,3612541,3612136,3612091,3612242,3612091,3612668,3612541,3612136,3612091,3612466,3612091,3612668,3612565,3612136,3612091,3612466,3612091,3612668,3612565,3612136,3612099,3612466,3612099,3612668,3612645,3612136,3612099,3612466,3612099,3612868,3612645,3612136,3612099,3612514,3612099,3612868,3612693,3612136,3612099,3612514,3612099,3612868,3612693,3612136,3612107,3612514,3612107,3612868,3612709,3612136,3612107,3612514,3612107,3612868,3612709,3612136,3612107,3612786,3612107,3612868,3613021,3612136,3612115,3612786,3612115,3612988,3612136,3612115,3612786,3612115,3612988,3612136,3612115,3612786,3612115,3612988,3612136,3612115,3612115,3612988,3612144,3612673,3612988,3612144,3612673,3612988,3612144,3612673,3612988,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612144,3612673,3612673,3612673,3612673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L13 W17/25; N=139; EHP=9151.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x17,normal:18x18,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x38,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x1</t>
+          <t>L13 W17/25; N=139; EHP=21421.451452; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x6,medium:123x7,normal:17x17,normal:18x18,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3614136,3614673,3614242,3614019,3614668,3614253,3614136,3614673,3614242,3614019,3614668,3614253,3614136,3614673,3614242,3614019,3614668,3614325,3614136,3614673,3614242,3614019,3614668,3614325,3614136,3614673,3614466,3614091,3614668,3614541,3614136,3614673,3614466,3614091,3614668,3614541,3614136,3614673,3614466,3614091,3614668,3614565,3614136,3614673,3614466,3614099,3614868,3614645,3614136,3614673,3614514,3614099,3614868,3614645,3614136,3614673,3614514,3614099,3614868,3614693,3614136,3614673,3614514,3614099,3614868,3614693,3614136,3614673,3614514,3614107,3614868,3614709,3614136,3614673,3614514,3614107,3614868,3614709,3614136,3614673,3614786,3614107,3614868,3615021,3614136,3614673,3614786,3614115,3614988,3614136,3614673,3614786,3614115,3614988,3614136,3614673,3614786,3614115,3614988,3614136,3614673,3614988,3614144,3614673,3614988,3614144,3614673,3614988,3614144,3614673,3614988,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614673,3614673,3614673,3614673</t>
+          <t>3614136,3614019,3614242,3614019,3614668,3614253,3614136,3614019,3614242,3614019,3614668,3614253,3614136,3614019,3614242,3614019,3614668,3614325,3614136,3614019,3614242,3614019,3614668,3614325,3614136,3614091,3614466,3614091,3614668,3614541,3614136,3614091,3614466,3614091,3614668,3614541,3614136,3614091,3614466,3614091,3614668,3614565,3614136,3614099,3614466,3614099,3614868,3614645,3614136,3614099,3614514,3614099,3614868,3614645,3614136,3614099,3614514,3614099,3614868,3614693,3614136,3614099,3614514,3614099,3614868,3614693,3614136,3614107,3614514,3614107,3614868,3614709,3614136,3614107,3614514,3614107,3614868,3614709,3614136,3614107,3614786,3614107,3614868,3615021,3614136,3614115,3614786,3614115,3614988,3614136,3614115,3614786,3614115,3614988,3614136,3614115,3614786,3614115,3614988,3614136,3614673,3614988,3614144,3614673,3614988,3614144,3614673,3614988,3614144,3614673,3614988,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614144,3614673,3614673,3614673,3614673,3614673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L13 W18/25; N=145; EHP=9778.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x1</t>
+          <t>L13 W18/25; N=145; EHP=22876.646366; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3616136,3616673,3616242,3616019,3616668,3616253,3616136,3616673,3616242,3616019,3616668,3616253,3616136,3616673,3616242,3616019,3616668,3616325,3616136,3616673,3616242,3616019,3616668,3616325,3616136,3616673,3616242,3616091,3616668,3616541,3616136,3616673,3616466,3616091,3616668,3616565,3616136,3616673,3616466,3616091,3616668,3616565,3616136,3616673,3616466,3616091,3616868,3616645,3616136,3616673,3616466,3616099,3616868,3616645,3616136,3616673,3616514,3616099,3616868,3616693,3616136,3616673,3616514,3616099,3616868,3616693,3616136,3616673,3616514,3616107,3616868,3616709,3616136,3616673,3616514,3616107,3616868,3616709,3616136,3616673,3616786,3616107,3616868,3617021,3616136,3616673,3616786,3616107,3616868,3617021,3616136,3616673,3616786,3616115,3616988,3616136,3616673,3616786,3616115,3616988,3616136,3616673,3616786,3616115,3616988,3616144,3616673,3616988,3616144,3616673,3616988,3616144,3616673,3616988,3616144,3616673,3616988,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616673,3616673,3616673,3616673,3616673,3616673</t>
+          <t>3616136,3616019,3616242,3616019,3616668,3616253,3616136,3616019,3616242,3616019,3616668,3616253,3616136,3616019,3616242,3616019,3616668,3616325,3616136,3616019,3616242,3616019,3616668,3616325,3616136,3616091,3616242,3616091,3616668,3616541,3616136,3616091,3616466,3616091,3616668,3616565,3616136,3616091,3616466,3616091,3616668,3616565,3616136,3616091,3616466,3616091,3616868,3616645,3616136,3616099,3616466,3616099,3616868,3616645,3616136,3616099,3616514,3616099,3616868,3616693,3616136,3616099,3616514,3616099,3616868,3616693,3616136,3616107,3616514,3616107,3616868,3616709,3616136,3616107,3616514,3616107,3616868,3616709,3616136,3616107,3616786,3616107,3616868,3617021,3616136,3616107,3616786,3616107,3616868,3617021,3616136,3616115,3616786,3616115,3616988,3616136,3616115,3616786,3616115,3616988,3616136,3616115,3616786,3616115,3616988,3616144,3616673,3616988,3616144,3616673,3616988,3616144,3616673,3616988,3616144,3616673,3616988,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616144,3616673,3616673,3616673,3616673,3616673,3616673,3616673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L13 W19/25; N=151; EHP=11325.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x18,normal:18x18,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L13 W19/25; N=151; EHP=26500.454183; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x5,fast:58x4,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x7,normal:17x18,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3618136,3618673,3618242,3618019,3618668,3618253,3618542,3618136,3618673,3618242,3618019,3618668,3618253,3618136,3618673,3618242,3618019,3618668,3618325,3618136,3618673,3618242,3618091,3618668,3618325,3618136,3618673,3618466,3618091,3618668,3618541,3618136,3618673,3618466,3618091,3618668,3618541,3618136,3618673,3618466,3618091,3618668,3618565,3618136,3618673,3618466,3618099,3618668,3618565,3618136,3618673,3618466,3618099,3618868,3618645,3618136,3618673,3618514,3618099,3618868,3618645,3618136,3618673,3618514,3618099,3618868,3618693,3618136,3618673,3618514,3618107,3618868,3618693,3618136,3618673,3618514,3618107,3618868,3618709,3618136,3618673,3618786,3618107,3618868,3619021,3618136,3618673,3618786,3618107,3618868,3619021,3618136,3618673,3618786,3618115,3618988,3618136,3618673,3618786,3618115,3618988,3618136,3618673,3618786,3618115,3618988,3618136,3618673,3618115,3618988,3618144,3618673,3618988,3618144,3618673,3618988,3618144,3618673,3618988,3618144,3618673,3618988,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618673,3618673,3618673,3618673,3618673</t>
+          <t>3618136,3618019,3618242,3618019,3618668,3618253,3618542,3618136,3618019,3618242,3618019,3618668,3618253,3618136,3618019,3618242,3618019,3618668,3618325,3618136,3618091,3618242,3618091,3618668,3618325,3618136,3618091,3618466,3618091,3618668,3618541,3618136,3618091,3618466,3618091,3618668,3618541,3618136,3618091,3618466,3618091,3618668,3618565,3618136,3618099,3618466,3618099,3618668,3618565,3618136,3618099,3618466,3618099,3618868,3618645,3618136,3618099,3618514,3618099,3618868,3618645,3618136,3618099,3618514,3618099,3618868,3618693,3618136,3618107,3618514,3618107,3618868,3618693,3618136,3618107,3618514,3618107,3618868,3618709,3618136,3618107,3618786,3618107,3618868,3619021,3618136,3618107,3618786,3618107,3618868,3619021,3618136,3618115,3618786,3618115,3618988,3618136,3618115,3618786,3618115,3618988,3618136,3618115,3618786,3618115,3618988,3618136,3618115,3618115,3618988,3618144,3618673,3618988,3618144,3618673,3618988,3618144,3618673,3618988,3618144,3618673,3618988,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618144,3618673,3618673,3618673,3618673,3618673,3618673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L13 W20/25; N=157; EHP=19016.000000; air:2x3,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x1,fast:98x5,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L13 W20/25; N=157; EHP=44494.725677; air:2x6,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017705,10017715,10017707,10048590,10017714,10017708,10017705,10017715,10017707,10048590,10017714,10017708,10017705,10017715,10017707,10048590,10017714,10017709,10017705,10017715,10017707,10048590,10017714,10017709,10017705,10017715,10017707,10017702,10017714,10017712,10017705,10017715,10017710,10017702,10017714,10017712,10017705,10017715,10017710,10017702,10017714,10017713,10017705,10017715,10017710,10017702,10017714,10017713,10017705,10017715,10017710,10048591,10017719,10045176,10017705,10017715,10017710,10048591,10017719,10045176,10017705,10017715,10017711,10048591,10017719,10017716,10017705,10017715,10017711,10048591,10017719,10017716,10017705,10017715,10017711,10017703,10017719,10017717,10017705,10017715,10017711,10017703,10017719,10017717,10017705,10017715,10017711,10017703,10017719,10017721,10017705,10017715,10017718,10017703,10017719,10017721,10017705,10017715,10017718,10017704,10017720,10017705,10017715,10017718,10017704,10017720,10017705,10017715,10017718,10017704,10017720,10017706,10017715,10017704,10017720,10017706,10017715,10017720,10017706,10017715,10017720,10017706,10017715,10017720,10017706,10017715,10017720,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017715,10017715,10017715,10017715,10017715,10017715</t>
+          <t>10017705,10048590,10017707,10048590,10017714,10017708,10017705,10048590,10017707,10048590,10017714,10017708,10017705,10048590,10017707,10048590,10017714,10017709,10017705,10048590,10017707,10048590,10017714,10017709,10017705,10017702,10017707,10017702,10017714,10017712,10017705,10017702,10017710,10017702,10017714,10017712,10017705,10017702,10017710,10017702,10017714,10017713,10017705,10017702,10017710,10017702,10017714,10017713,10017705,10048591,10017710,10048591,10017719,10045176,10017705,10048591,10017710,10048591,10017719,10045176,10017705,10048591,10017711,10048591,10017719,10017716,10017705,10048591,10017711,10048591,10017719,10017716,10017705,10017703,10017711,10017703,10017719,10017717,10017705,10017703,10017711,10017703,10017719,10017717,10017705,10017703,10017711,10017703,10017719,10017721,10017705,10017703,10017718,10017703,10017719,10017721,10017705,10017704,10017718,10017704,10017720,10017705,10017704,10017718,10017704,10017720,10017705,10017704,10017718,10017704,10017720,10017706,10017704,10017704,10017720,10017706,10017715,10017720,10017706,10017715,10017720,10017706,10017715,10017720,10017706,10017715,10017720,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017706,10017715,10017715,10017715,10017715,10017715,10017715,10017715</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L13 W21/25; N=163; EHP=19397.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L13 W21/25; N=163; EHP=45404.549580; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017725,10017736,10017727,10048592,10017735,10017728,10017725,10017736,10017727,10048592,10017735,10017728,10017725,10017736,10017727,10048592,10017735,10017729,10017725,10017736,10017727,10048592,10017735,10017729,10017725,10017736,10017727,10017722,10017735,10017732,10017725,10017736,10017730,10017722,10017735,10017732,10017725,10017736,10017730,10017722,10017735,10017733,10017725,10017736,10017730,10017722,10017735,10017733,10017725,10017736,10017730,10048593,10017739,10017734,10017725,10017736,10017730,10048593,10017739,10017734,10017725,10017736,10017731,10048593,10017739,10045177,10017725,10017736,10017731,10048593,10017739,10045177,10017725,10017736,10017731,10017723,10017739,10017737,10017725,10017736,10017731,10017723,10017739,10017737,10017725,10017736,10017731,10017723,10017739,10017741,10017725,10017736,10017738,10017723,10017739,10017741,10017725,10017736,10017738,10017724,10017739,10017725,10017736,10017738,10017724,10017740,10017725,10017736,10017738,10017724,10017740,10017725,10017736,10017738,10017724,10017740,10017725,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017736,10017736,10017736,10017736,10017736,10017736</t>
+          <t>10017725,10048592,10017727,10048592,10017735,10017728,10017725,10048592,10017727,10048592,10017735,10017728,10017725,10048592,10017727,10048592,10017735,10017729,10017725,10048592,10017727,10048592,10017735,10017729,10017725,10017722,10017727,10017722,10017735,10017732,10017725,10017722,10017730,10017722,10017735,10017732,10017725,10017722,10017730,10017722,10017735,10017733,10017725,10017722,10017730,10017722,10017735,10017733,10017725,10048593,10017730,10048593,10017739,10017734,10017725,10048593,10017730,10048593,10017739,10017734,10017725,10048593,10017731,10048593,10017739,10045177,10017725,10048593,10017731,10048593,10017739,10045177,10017725,10017723,10017731,10017723,10017739,10017737,10017725,10017723,10017731,10017723,10017739,10017737,10017725,10017723,10017731,10017723,10017739,10017741,10017725,10017723,10017738,10017723,10017739,10017741,10017725,10017724,10017738,10017724,10017739,10017725,10017724,10017738,10017724,10017740,10017725,10017724,10017738,10017724,10017740,10017725,10017724,10017738,10017724,10017740,10017725,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017740,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017726,10017736,10017736,10017736,10017736,10017736,10017736,10017736</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L13 W22/25; N=169; EHP=19785.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L13 W22/25; N=169; EHP=46294.741795; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x8,normal:17x21,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017745,10017755,10017747,10048594,10017754,10045178,10017745,10017755,10017747,10048594,10017754,10045178,10017745,10017755,10017747,10048594,10017754,10017748,10017745,10017755,10017747,10048594,10017754,10017748,10017745,10017755,10017747,10017742,10017754,10017748,10017745,10017755,10017747,10017742,10017754,10017751,10017745,10017755,10017749,10017742,10017754,10017751,10017745,10017755,10017749,10017742,10017754,10017752,10017745,10017755,10017749,10048595,10017754,10017752,10017745,10017755,10017749,10048595,10017759,10017753,10017745,10017755,10017749,10048595,10017759,10017753,10017745,10017755,10017750,10048595,10017759,10017756,10017745,10017755,10017750,10048595,10017759,10017756,10017745,10017755,10017750,10017743,10017759,10017757,10017745,10017755,10017750,10017743,10017759,10017757,10017745,10017755,10017750,10017743,10017759,10017761,10017745,10017755,10017758,10017743,10017759,10017761,10017745,10017755,10017758,10017744,10017760,10017745,10017755,10017758,10017744,10017760,10017745,10017755,10017758,10017744,10017760,10017746,10017755,10017758,10017744,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017755,10017755,10017755,10017755,10017755,10017755,10017755,10017755</t>
+          <t>10017745,10048594,10017747,10048594,10017754,10045178,10017745,10048594,10017747,10048594,10017754,10045178,10017745,10048594,10017747,10048594,10017754,10017748,10017745,10048594,10017747,10048594,10017754,10017748,10017745,10017742,10017747,10017742,10017754,10017748,10017745,10017742,10017747,10017742,10017754,10017751,10017745,10017742,10017749,10017742,10017754,10017751,10017745,10017742,10017749,10017742,10017754,10017752,10017745,10048595,10017749,10048595,10017754,10017752,10017745,10048595,10017749,10048595,10017759,10017753,10017745,10048595,10017749,10048595,10017759,10017753,10017745,10048595,10017750,10048595,10017759,10017756,10017745,10048595,10017750,10048595,10017759,10017756,10017745,10017743,10017750,10017743,10017759,10017757,10017745,10017743,10017750,10017743,10017759,10017757,10017745,10017743,10017750,10017743,10017759,10017761,10017745,10017743,10017758,10017743,10017759,10017761,10017745,10017744,10017758,10017744,10017760,10017745,10017744,10017758,10017744,10017760,10017745,10017744,10017758,10017744,10017760,10017746,10017744,10017758,10017744,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017760,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017746,10017755,10017755,10017755,10017755,10017755,10017755,10017755,10017755,10017755</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L13 W23/25; N=175; EHP=20181.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L13 W23/25; N=175; EHP=47227.971387; air:2x8,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x9,normal:17x20,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017765,10017775,10017767,10048596,10017774,10017768,10017765,10017775,10017767,10048596,10017774,10017768,10017765,10017775,10017767,10048596,10017774,10045179,10017765,10017775,10017767,10048596,10017774,10045179,10017765,10017775,10017767,10048596,10017774,10017771,10017765,10017775,10017769,10017762,10017774,10017771,10017765,10017775,10017769,10017762,10017774,10017772,10017765,10017775,10017769,10017762,10017774,10017772,10017765,10017775,10017769,10017762,10017774,10017772,10017765,10017775,10017769,10048597,10017779,10017773,10017765,10017775,10017770,10048597,10017779,10017773,10017765,10017775,10017770,10048597,10017779,10017776,10017765,10017775,10017770,10048597,10017779,10017776,10017765,10017775,10017770,10017763,10017779,10017777,10017765,10017775,10017770,10017763,10017779,10017777,10017765,10017775,10017778,10017763,10017779,10017781,10017765,10017775,10017778,10017763,10017779,10017781,10017765,10017775,10017778,10017763,10017779,10017781,10017765,10017775,10017778,10017764,10017780,10017765,10017775,10017778,10017764,10017780,10017765,10017775,10017778,10017764,10017780,10017765,10017775,10017764,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017775,10017775,10017775,10017775,10017775,10017775,10017775</t>
+          <t>10017765,10048596,10017767,10048596,10017774,10017768,10017765,10048596,10017767,10048596,10017774,10017768,10017765,10048596,10017767,10048596,10017774,10045179,10017765,10048596,10017767,10048596,10017774,10045179,10017765,10048596,10017767,10048596,10017774,10017771,10017765,10017762,10017769,10017762,10017774,10017771,10017765,10017762,10017769,10017762,10017774,10017772,10017765,10017762,10017769,10017762,10017774,10017772,10017765,10017762,10017769,10017762,10017774,10017772,10017765,10048597,10017769,10048597,10017779,10017773,10017765,10048597,10017770,10048597,10017779,10017773,10017765,10048597,10017770,10048597,10017779,10017776,10017765,10048597,10017770,10048597,10017779,10017776,10017765,10017763,10017770,10017763,10017779,10017777,10017765,10017763,10017770,10017763,10017779,10017777,10017765,10017763,10017778,10017763,10017779,10017781,10017765,10017763,10017778,10017763,10017779,10017781,10017765,10017763,10017778,10017763,10017779,10017781,10017765,10017764,10017778,10017764,10017780,10017765,10017764,10017778,10017764,10017780,10017765,10017764,10017778,10017764,10017780,10017765,10017764,10017764,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017780,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017766,10017775,10017775,10017775,10017775,10017775,10017775,10017775,10017775</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L13 W24/25; N=181; EHP=21610.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x3</t>
+          <t>L13 W24/25; N=181; EHP=50577.209426; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017785,10017796,10017787,10048598,10017795,10017788,10017802,10017785,10017796,10017787,10048598,10017795,10017788,10017785,10017796,10017787,10048598,10017795,10017789,10017785,10017796,10017787,10048598,10017795,10017789,10017785,10017796,10017787,10017782,10017795,10017792,10017785,10017796,10017790,10017782,10017795,10017792,10017785,10017796,10017790,10017782,10017795,10017792,10017785,10017796,10017790,10017782,10017795,10017793,10017785,10017796,10017790,10017782,10017795,10017793,10017785,10017796,10017790,10048599,10017800,10017793,10017785,10017796,10017790,10048599,10017800,10017794,10017785,10017796,10017791,10048599,10017800,10017794,10017785,10017796,10017791,10048599,10017800,10017797,10017785,10017796,10017791,10017783,10017800,10017797,10017785,10017796,10017791,10017783,10017800,10017798,10017785,10017796,10017791,10017783,10017800,10017798,10017785,10017796,10017791,10017783,10017800,10045180,10017785,10017796,10017799,10017783,10017800,10045180,10017785,10017796,10017799,10017784,10017800,10017785,10017796,10017799,10017784,10017801,10017785,10017796,10017799,10017784,10017801,10017785,10017796,10017799,10017784,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017796,10017796,10017796,10017796,10017796,10017796,10017796,10017796</t>
+          <t>10017785,10048598,10017787,10048598,10017795,10017788,10017802,10017785,10048598,10017787,10048598,10017795,10017788,10017785,10048598,10017787,10048598,10017795,10017789,10017785,10048598,10017787,10048598,10017795,10017789,10017785,10017782,10017787,10017782,10017795,10017792,10017785,10017782,10017790,10017782,10017795,10017792,10017785,10017782,10017790,10017782,10017795,10017792,10017785,10017782,10017790,10017782,10017795,10017793,10017785,10017782,10017790,10017782,10017795,10017793,10017785,10048599,10017790,10048599,10017800,10017793,10017785,10048599,10017790,10048599,10017800,10017794,10017785,10048599,10017791,10048599,10017800,10017794,10017785,10048599,10017791,10048599,10017800,10017797,10017785,10017783,10017791,10017783,10017800,10017797,10017785,10017783,10017791,10017783,10017800,10017798,10017785,10017783,10017791,10017783,10017800,10017798,10017785,10017783,10017791,10017783,10017800,10045180,10017785,10017783,10017799,10017783,10017800,10045180,10017785,10017784,10017799,10017784,10017800,10017785,10017784,10017799,10017784,10017801,10017785,10017784,10017799,10017784,10017801,10017785,10017784,10017799,10017784,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017801,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017786,10017796,10017796,10017796,10017796,10017796,10017796,10017796,10017796,10017796</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L13 W25/25; N=187; EHP=43134.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x2,heavy:88x2,fast:98x5,medium:108x10,medium:123x9,heavy:127x2,boss:130x1</t>
+          <t>L13 W25/25; N=187; EHP=100895.452563; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,boss:130x1,fast:30x5,fast:58x6,fast:64x6,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x10,medium:123x9,normal:17x22,normal:18x22,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L13/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L13/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>249</v>
+        <v>300</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>235</v>
+        <v>350</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>221</v>
+        <v>340</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>193</v>
+        <v>280</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>186</v>
+        <v>260</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>172</v>
+        <v>350</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>158</v>
+        <v>230</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>144</v>
+        <v>280</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>137</v>
+        <v>250</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>350</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>240</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
